--- a/data/templates/PubMed-Enrichment.xlsx
+++ b/data/templates/PubMed-Enrichment.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publication" sheetId="1" r:id="R29cf1875df9f4dfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repository Records" sheetId="2" r:id="R1b1e4d31891947b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SRA Accessions" sheetId="3" r:id="R983437c5590c4b3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MeSH" sheetId="4" r:id="Rfcfba102cbbe4991"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MeSH Links" sheetId="5" r:id="R79b07a17b7544b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publication" sheetId="1" r:id="R1c2f5f28d4534e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repository Records" sheetId="2" r:id="Rc287d6df0e764e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SRA Accessions" sheetId="3" r:id="R33237f365840400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MeSH" sheetId="4" r:id="R974c00ad21f84284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MeSH Links" sheetId="5" r:id="R97ecb6dc90c54ede"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,6 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="@"/>
+  </x:numFmts>
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
@@ -48,9 +51,21 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -253,27 +268,27 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>PMID</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>DOI</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>PMCID</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Title</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Publication Date</x:v>
       </x:c>
     </x:row>
@@ -286,35 +301,35 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="52" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>PMID</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Resource</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Accession</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Native Entity Level</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Reported Data Type</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Title</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Description</x:v>
       </x:c>
     </x:row>
@@ -327,35 +342,35 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>PMID</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Experiment Accession</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Study Accession</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Sample Accession</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>BioSample Accession</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>BioProject Accession</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Run Accession</x:v>
       </x:c>
     </x:row>
@@ -368,31 +383,31 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Descriptor UI</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Descriptor</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Qualifier UI</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Qualifier</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Publication Count</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Associated PMIDs</x:v>
       </x:c>
     </x:row>
@@ -405,27 +420,27 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>PMID</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Descriptor UI</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Qualifier UI</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Descriptor Major Topic</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Qualifier Major Topic</x:v>
       </x:c>
     </x:row>
